--- a/output/pdf_financials_xlsx/PSE.xlsx
+++ b/output/pdf_financials_xlsx/PSE.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.157117</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.157117</v>
       </c>
     </row>
     <row r="93">
@@ -2854,7 +2854,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>2.157117</v>
       </c>

--- a/output/pdf_financials_xlsx/PSE.xlsx
+++ b/output/pdf_financials_xlsx/PSE.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.049926</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1.583656</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-2.049926</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-1.583656</v>
       </c>
     </row>
     <row r="12">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.177278</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.194888</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.177278</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.194888</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.319879</v>
+        <v>0.142601</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.642288</v>
+        <v>0.4474</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">

--- a/output/pdf_financials_xlsx/PSE.xlsx
+++ b/output/pdf_financials_xlsx/PSE.xlsx
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.162445</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.1716</v>
       </c>
     </row>
     <row r="68">
